--- a/.data/birthdays.xlsx
+++ b/.data/birthdays.xlsx
@@ -2,17 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anniversaires" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Anniversaires'!$A$1:$E$311</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Anniversaires'!$A$1:$E$310</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -28,8 +27,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -41,8 +42,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002D3748"/>
-        <bgColor rgb="002D3748"/>
+        <fgColor rgb="FF2D3748"/>
+        <bgColor rgb="FF2D3748"/>
       </patternFill>
     </fill>
   </fills>
@@ -65,7 +66,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -428,12 +429,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E311"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E349"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="2" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bde Ensae</t>
+          <t>Didi Diouf</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -477,75 +477,70 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Didi Diouf</t>
+          <t>Lise Kelchlin</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lise Kelchlin</t>
+          <t>Genevieve Ebert</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Genevieve Ebert</t>
+          <t>Vincent Margerin</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>6</v>
+      </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vincent Margerin</t>
+          <t>Hugo Kvl</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>7</v>
+      </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
@@ -553,16 +548,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hugo Kvl</t>
+          <t>Oceane de Moras</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>12</v>
+      </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
@@ -570,84 +564,79 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oceane de Moras</t>
+          <t>Thomas Dori</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>13</v>
+      </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Thomas Dori</t>
+          <t>Medjo Wf</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>16</v>
+      </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Medjo Wf</t>
+          <t>Ralph Egbert Schmitt-Nilson</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>18</v>
+      </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ralph Egbert Schmitt-Nilson</t>
+          <t>Louis Pierart</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>19</v>
+      </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Louis Pierart</t>
+          <t>Marie Guezennec</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>20</v>
+      </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
@@ -655,16 +644,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marie Guezennec</t>
+          <t>Thibault Baron</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>24</v>
+      </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
@@ -672,16 +660,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Thibault Baron</t>
+          <t>Thomas Pereira</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>27</v>
+      </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
@@ -689,24 +676,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Thomas Pereira</t>
+          <t>Marion Paclot</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>31</v>
+      </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marion Paclot</t>
+          <t>Thomas Lesgourgues</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -715,66 +701,62 @@
       <c r="C16" t="n">
         <v>31</v>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Thomas Lesgourgues</t>
+          <t>Helene de Montmarin</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Helene de Montmarin</t>
+          <t>Zeineb Lassoued</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Zeineb Lassoued</t>
+          <t>Florian Martineau</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Florian Martineau</t>
+          <t>Jalal Kai</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -783,58 +765,54 @@
       <c r="C20" t="n">
         <v>4</v>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jalal Kai</t>
+          <t>Camille Coupez</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>8</v>
+      </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Camille Coupez</t>
+          <t>Marcos Lorenzo</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>9</v>
+      </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marcos Lorenzo</t>
+          <t>Saber Trabelsi</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+        <v>10</v>
+      </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
@@ -842,7 +820,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Saber Trabelsi</t>
+          <t>Sophie Bory</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -851,58 +829,54 @@
       <c r="C24" t="n">
         <v>10</v>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sophie Bory</t>
+          <t>Ladislas de Guerre</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>12</v>
+      </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ladislas de Guerre</t>
+          <t>Pablo Mskl</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
+        <v>15</v>
+      </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pablo Mskl</t>
+          <t>Christoph Ha</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>15</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
+        <v>16</v>
+      </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
@@ -910,33 +884,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Christoph Ha</t>
+          <t>Marion Chich</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+        <v>17</v>
+      </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marion Chich</t>
+          <t>Hinarii Pichevin</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
+        <v>18</v>
+      </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
@@ -944,7 +916,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hinarii Pichevin</t>
+          <t>Paul Ca</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -953,58 +925,54 @@
       <c r="C30" t="n">
         <v>18</v>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Paul Ca</t>
+          <t>Hamza Akasbi</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>18</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
+        <v>21</v>
+      </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hamza Akasbi</t>
+          <t>Taige Zhang</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>21</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
+        <v>23</v>
+      </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Taige Zhang</t>
+          <t>Kelly Amzallag</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>23</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
+        <v>24</v>
+      </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
@@ -1012,16 +980,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kelly Amzallag</t>
+          <t>Sylvain Sertillanges</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>24</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
+        <v>27</v>
+      </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
@@ -1029,16 +996,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sylvain Sertillanges</t>
+          <t>Cecile Ebert</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>27</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
+        <v>28</v>
+      </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
@@ -1046,7 +1012,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cecile Dame Ginette</t>
+          <t>Mohamed Benkhalfa</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1055,7 +1021,6 @@
       <c r="C36" t="n">
         <v>28</v>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>1</v>
       </c>
@@ -1063,50 +1028,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mohamed Benkhalfa</t>
+          <t>Stephane Savouroux</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>28</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Stephane Savouroux</t>
+          <t>Emilie Trellu</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Emilie Trellu</t>
+          <t>Thibault Antoine</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
+        <v>5</v>
+      </c>
       <c r="E39" t="n">
         <v>1</v>
       </c>
@@ -1114,24 +1076,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Thibault Antoine</t>
+          <t>Erwan Rxl</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
+        <v>7</v>
+      </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Erwan Rxl</t>
+          <t>Timothee Consigny</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1140,32 +1101,30 @@
       <c r="C41" t="n">
         <v>7</v>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Timothee Consigny</t>
+          <t>Hend Turki</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>7</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
+        <v>9</v>
+      </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hend Turki</t>
+          <t>Marion Rasengan</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1174,32 +1133,30 @@
       <c r="C43" t="n">
         <v>9</v>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marion Rasengan</t>
+          <t>Michel Stofer</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>9</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
+        <v>10</v>
+      </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Michel Stofer</t>
+          <t>Sofiane Belalia</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1208,7 +1165,6 @@
       <c r="C45" t="n">
         <v>10</v>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
         <v>1</v>
       </c>
@@ -1216,58 +1172,55 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sofiane Belalia</t>
+          <t>François Penet</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>10</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
+        <v>11</v>
+      </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>François Penet</t>
+          <t>Bruce Hazan</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>3</v>
       </c>
       <c r="C47" t="n">
-        <v>11</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
+        <v>12</v>
+      </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bruce Hazan</t>
+          <t>Jeremy Planul</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>12</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
+        <v>13</v>
+      </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jeremy Planul</t>
+          <t>Laura V'you</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1276,7 +1229,6 @@
       <c r="C49" t="n">
         <v>13</v>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
         <v>1</v>
       </c>
@@ -1284,7 +1236,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Laura V'you</t>
+          <t>Melodie Dalle</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1293,7 +1245,6 @@
       <c r="C50" t="n">
         <v>13</v>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
         <v>1</v>
       </c>
@@ -1301,16 +1252,15 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Melodie Dalle</t>
+          <t>Chant Montana</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>3</v>
       </c>
       <c r="C51" t="n">
-        <v>13</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
+        <v>14</v>
+      </c>
       <c r="E51" t="n">
         <v>1</v>
       </c>
@@ -1318,16 +1268,15 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Chant Montana</t>
+          <t>Aurele Fontaine</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>14</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
+        <v>15</v>
+      </c>
       <c r="E52" t="n">
         <v>1</v>
       </c>
@@ -1335,16 +1284,15 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Aurele Fontaine</t>
+          <t>Valentin Amiot</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>15</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
+        <v>18</v>
+      </c>
       <c r="E53" t="n">
         <v>1</v>
       </c>
@@ -1352,16 +1300,15 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Valentin Amiot</t>
+          <t>Heene Huiier</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>3</v>
       </c>
       <c r="C54" t="n">
-        <v>18</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+        <v>22</v>
+      </c>
       <c r="E54" t="n">
         <v>1</v>
       </c>
@@ -1369,16 +1316,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Heene Huiier</t>
+          <t>Gilles Kant</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>3</v>
       </c>
       <c r="C55" t="n">
-        <v>22</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+        <v>25</v>
+      </c>
       <c r="E55" t="n">
         <v>1</v>
       </c>
@@ -1386,16 +1332,15 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gilles Kant</t>
+          <t>Philippe Mgtn</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>3</v>
       </c>
       <c r="C56" t="n">
-        <v>25</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
+        <v>26</v>
+      </c>
       <c r="E56" t="n">
         <v>1</v>
       </c>
@@ -1403,16 +1348,15 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Philippe Mgtn</t>
+          <t>Carole Mery</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>3</v>
       </c>
       <c r="C57" t="n">
-        <v>26</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
+        <v>27</v>
+      </c>
       <c r="E57" t="n">
         <v>1</v>
       </c>
@@ -1420,16 +1364,15 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Carole Mery</t>
+          <t>Ines Garnier</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>3</v>
       </c>
       <c r="C58" t="n">
-        <v>27</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
+        <v>28</v>
+      </c>
       <c r="E58" t="n">
         <v>1</v>
       </c>
@@ -1437,16 +1380,15 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ines Garnier</t>
+          <t>Olivier Grave</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>3</v>
       </c>
       <c r="C59" t="n">
-        <v>28</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
+        <v>30</v>
+      </c>
       <c r="E59" t="n">
         <v>1</v>
       </c>
@@ -1454,16 +1396,15 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Olivier Grave</t>
+          <t>Alinka Kalinka</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>30</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="E60" t="n">
         <v>1</v>
       </c>
@@ -1471,7 +1412,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alinka Kalinka</t>
+          <t>Benjamin Pontier</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1480,7 +1421,6 @@
       <c r="C61" t="n">
         <v>1</v>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
         <v>1</v>
       </c>
@@ -1488,16 +1428,15 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Benjamin Pontier</t>
+          <t>Marion Saurel</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="E62" t="n">
         <v>1</v>
       </c>
@@ -1505,16 +1444,15 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Marion Saurel</t>
+          <t>Laure Teillet</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="E63" t="n">
         <v>1</v>
       </c>
@@ -1522,7 +1460,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Laure Teillet</t>
+          <t>William Kunter</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1531,7 +1469,6 @@
       <c r="C64" t="n">
         <v>3</v>
       </c>
-      <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
         <v>1</v>
       </c>
@@ -1539,16 +1476,15 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>William Kunter</t>
+          <t>Celine Ebert</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
+        <v>6</v>
+      </c>
       <c r="E65" t="n">
         <v>1</v>
       </c>
@@ -1556,7 +1492,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Celine Ebert</t>
+          <t>Guillaume Roussellet</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1565,7 +1501,6 @@
       <c r="C66" t="n">
         <v>6</v>
       </c>
-      <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
         <v>1</v>
       </c>
@@ -1573,7 +1508,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Guillaume Roussellet</t>
+          <t>Wassel Touil</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1582,7 +1517,6 @@
       <c r="C67" t="n">
         <v>6</v>
       </c>
-      <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
         <v>1</v>
       </c>
@@ -1590,16 +1524,15 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Wassel Touil</t>
+          <t>Laurent Faure</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
+        <v>7</v>
+      </c>
       <c r="E68" t="n">
         <v>1</v>
       </c>
@@ -1607,16 +1540,15 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Laurent Faure</t>
+          <t>Marion Collier</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
+        <v>11</v>
+      </c>
       <c r="E69" t="n">
         <v>1</v>
       </c>
@@ -1624,16 +1556,15 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Marion Collier</t>
+          <t>Caroline Clement Perret</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
+        <v>12</v>
+      </c>
       <c r="E70" t="n">
         <v>1</v>
       </c>
@@ -1641,7 +1572,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Caroline Clement Perret</t>
+          <t>Mackieh Maximus</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1650,7 +1581,6 @@
       <c r="C71" t="n">
         <v>12</v>
       </c>
-      <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
         <v>1</v>
       </c>
@@ -1658,7 +1588,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mackieh Maximus</t>
+          <t>Pierre-Edouard Collignon</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1667,7 +1597,6 @@
       <c r="C72" t="n">
         <v>12</v>
       </c>
-      <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
         <v>1</v>
       </c>
@@ -1675,16 +1604,15 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Pierre-Edouard Collignon</t>
+          <t>Bastien Roleau</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>4</v>
       </c>
       <c r="C73" t="n">
-        <v>12</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
+        <v>15</v>
+      </c>
       <c r="E73" t="n">
         <v>1</v>
       </c>
@@ -1692,7 +1620,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Bastien Roleau</t>
+          <t>Maxime Brun</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1701,7 +1629,6 @@
       <c r="C74" t="n">
         <v>15</v>
       </c>
-      <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
         <v>1</v>
       </c>
@@ -1709,7 +1636,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Maxime Brun</t>
+          <t>Mickael BO</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1718,7 +1645,6 @@
       <c r="C75" t="n">
         <v>15</v>
       </c>
-      <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
         <v>1</v>
       </c>
@@ -1726,16 +1652,15 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mickael BO</t>
+          <t>Sylvie Tran</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>4</v>
       </c>
       <c r="C76" t="n">
-        <v>15</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
+        <v>17</v>
+      </c>
       <c r="E76" t="n">
         <v>1</v>
       </c>
@@ -1743,16 +1668,15 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sylvie Tran</t>
+          <t>Adelaïde Authier</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>17</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
+        <v>18</v>
+      </c>
       <c r="E77" t="n">
         <v>1</v>
       </c>
@@ -1760,7 +1684,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Adelaïde Authier</t>
+          <t>Thibault de Coincy</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1769,7 +1693,6 @@
       <c r="C78" t="n">
         <v>18</v>
       </c>
-      <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
         <v>1</v>
       </c>
@@ -1777,16 +1700,15 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Thibault de Coincy</t>
+          <t>Anastasia Odintsova</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>18</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
+        <v>19</v>
+      </c>
       <c r="E79" t="n">
         <v>1</v>
       </c>
@@ -1794,16 +1716,15 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Anastasia Odintsova</t>
+          <t>Adrien Lagarrigue</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>19</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
+        <v>20</v>
+      </c>
       <c r="E80" t="n">
         <v>1</v>
       </c>
@@ -1811,7 +1732,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Adrien Lagarrigue</t>
+          <t>Marie de Raismes</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1820,7 +1741,6 @@
       <c r="C81" t="n">
         <v>20</v>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
         <v>1</v>
       </c>
@@ -1828,7 +1748,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Marie de Raismes</t>
+          <t>Omar Chacha</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1837,7 +1757,6 @@
       <c r="C82" t="n">
         <v>20</v>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
         <v>1</v>
       </c>
@@ -1845,16 +1764,15 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Omar Chacha</t>
+          <t>Bernhard Ney</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>20</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
+        <v>21</v>
+      </c>
       <c r="E83" t="n">
         <v>1</v>
       </c>
@@ -1862,16 +1780,15 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Bernhard Ney</t>
+          <t>Esther Benchimol Aidan</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>4</v>
       </c>
       <c r="C84" t="n">
-        <v>21</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
+        <v>22</v>
+      </c>
       <c r="E84" t="n">
         <v>1</v>
       </c>
@@ -1879,16 +1796,15 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Esther Benchimol Aidan</t>
+          <t>Charlotte Mere</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>22</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
+        <v>24</v>
+      </c>
       <c r="E85" t="n">
         <v>1</v>
       </c>
@@ -1896,7 +1812,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Charlotte Mere</t>
+          <t>Selma Jaziri</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1905,7 +1821,6 @@
       <c r="C86" t="n">
         <v>24</v>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
         <v>1</v>
       </c>
@@ -1913,7 +1828,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Selma Jaziri</t>
+          <t>Sophie Lavaud</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1922,7 +1837,6 @@
       <c r="C87" t="n">
         <v>24</v>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
         <v>1</v>
       </c>
@@ -1930,16 +1844,15 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sophie Lavaud</t>
+          <t>Victor Owen</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>4</v>
       </c>
       <c r="C88" t="n">
-        <v>24</v>
-      </c>
-      <c r="D88" t="inlineStr"/>
+        <v>25</v>
+      </c>
       <c r="E88" t="n">
         <v>1</v>
       </c>
@@ -1947,16 +1860,15 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Victor Owen</t>
+          <t>Marion Ebert</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>4</v>
       </c>
       <c r="C89" t="n">
-        <v>25</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
+        <v>27</v>
+      </c>
       <c r="E89" t="n">
         <v>1</v>
       </c>
@@ -1964,7 +1876,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Marion Ebert</t>
+          <t>Richard Pierre</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -1973,7 +1885,6 @@
       <c r="C90" t="n">
         <v>27</v>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
         <v>1</v>
       </c>
@@ -1981,7 +1892,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Richard Pierre</t>
+          <t>So Laine</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -1990,7 +1901,6 @@
       <c r="C91" t="n">
         <v>27</v>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
         <v>1</v>
       </c>
@@ -1998,16 +1908,15 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>So Laine</t>
+          <t>Alexis Dupont</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>4</v>
       </c>
       <c r="C92" t="n">
-        <v>27</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
+        <v>30</v>
+      </c>
       <c r="E92" t="n">
         <v>1</v>
       </c>
@@ -2015,16 +1924,15 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Alexis Dupont</t>
+          <t>Bda Ensae</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C93" t="n">
-        <v>30</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="E93" t="n">
         <v>1</v>
       </c>
@@ -2032,16 +1940,15 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Bda Ensae</t>
+          <t>Amine Naouas</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>5</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="E94" t="n">
         <v>1</v>
       </c>
@@ -2049,16 +1956,15 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Amine Naouas</t>
+          <t>Dona Almosni</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>5</v>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
+        <v>6</v>
+      </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
@@ -2066,16 +1972,15 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Dona Almosni</t>
+          <t>Hind Bahhoussi</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>5</v>
       </c>
       <c r="C96" t="n">
-        <v>6</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
+        <v>11</v>
+      </c>
       <c r="E96" t="n">
         <v>1</v>
       </c>
@@ -2083,7 +1988,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Hind Bahhoussi</t>
+          <t>Sebastien Delucinge</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -2092,7 +1997,6 @@
       <c r="C97" t="n">
         <v>11</v>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
         <v>1</v>
       </c>
@@ -2100,16 +2004,15 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sebastien Delucinge</t>
+          <t>Sophie Blondel</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>5</v>
       </c>
       <c r="C98" t="n">
-        <v>11</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
+        <v>12</v>
+      </c>
       <c r="E98" t="n">
         <v>1</v>
       </c>
@@ -2117,7 +2020,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sophie Blondel</t>
+          <t>Yannick Benet MaBrik Immo</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -2126,7 +2029,6 @@
       <c r="C99" t="n">
         <v>12</v>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
         <v>1</v>
       </c>
@@ -2134,16 +2036,15 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Yannick Benet MaBrik Immo</t>
+          <t>Anne-Solene Husson</t>
         </is>
       </c>
       <c r="B100" t="n">
         <v>5</v>
       </c>
       <c r="C100" t="n">
-        <v>12</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
+        <v>16</v>
+      </c>
       <c r="E100" t="n">
         <v>1</v>
       </c>
@@ -2151,16 +2052,15 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Anne-Solene Husson</t>
+          <t>Vyx Ph</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>5</v>
       </c>
       <c r="C101" t="n">
-        <v>16</v>
-      </c>
-      <c r="D101" t="inlineStr"/>
+        <v>17</v>
+      </c>
       <c r="E101" t="n">
         <v>1</v>
       </c>
@@ -2168,16 +2068,15 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Vyx Ph</t>
+          <t>Gllt Vinc</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>5</v>
       </c>
       <c r="C102" t="n">
-        <v>17</v>
-      </c>
-      <c r="D102" t="inlineStr"/>
+        <v>19</v>
+      </c>
       <c r="E102" t="n">
         <v>1</v>
       </c>
@@ -2185,7 +2084,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Gllt Vinc</t>
+          <t>Thibaut Rc</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -2194,7 +2093,6 @@
       <c r="C103" t="n">
         <v>19</v>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
         <v>1</v>
       </c>
@@ -2202,16 +2100,15 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Thibaut Rc</t>
+          <t>Claire Prudhon</t>
         </is>
       </c>
       <c r="B104" t="n">
         <v>5</v>
       </c>
       <c r="C104" t="n">
-        <v>19</v>
-      </c>
-      <c r="D104" t="inlineStr"/>
+        <v>22</v>
+      </c>
       <c r="E104" t="n">
         <v>1</v>
       </c>
@@ -2219,16 +2116,15 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Claire Prudhon</t>
+          <t>Marie Grimond</t>
         </is>
       </c>
       <c r="B105" t="n">
         <v>5</v>
       </c>
       <c r="C105" t="n">
-        <v>22</v>
-      </c>
-      <c r="D105" t="inlineStr"/>
+        <v>23</v>
+      </c>
       <c r="E105" t="n">
         <v>1</v>
       </c>
@@ -2236,16 +2132,15 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Marie Grimond</t>
+          <t>Antwan Le Saint</t>
         </is>
       </c>
       <c r="B106" t="n">
         <v>5</v>
       </c>
       <c r="C106" t="n">
-        <v>23</v>
-      </c>
-      <c r="D106" t="inlineStr"/>
+        <v>25</v>
+      </c>
       <c r="E106" t="n">
         <v>1</v>
       </c>
@@ -2253,16 +2148,15 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Antwan Le Saint</t>
+          <t>Maxence Rbr</t>
         </is>
       </c>
       <c r="B107" t="n">
         <v>5</v>
       </c>
       <c r="C107" t="n">
-        <v>25</v>
-      </c>
-      <c r="D107" t="inlineStr"/>
+        <v>26</v>
+      </c>
       <c r="E107" t="n">
         <v>1</v>
       </c>
@@ -2270,16 +2164,15 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Maxence Rbr</t>
+          <t>Emm Ry</t>
         </is>
       </c>
       <c r="B108" t="n">
         <v>5</v>
       </c>
       <c r="C108" t="n">
-        <v>26</v>
-      </c>
-      <c r="D108" t="inlineStr"/>
+        <v>28</v>
+      </c>
       <c r="E108" t="n">
         <v>1</v>
       </c>
@@ -2287,16 +2180,15 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Emm Ry</t>
+          <t>Sandrine Benichou</t>
         </is>
       </c>
       <c r="B109" t="n">
         <v>5</v>
       </c>
       <c r="C109" t="n">
-        <v>28</v>
-      </c>
-      <c r="D109" t="inlineStr"/>
+        <v>29</v>
+      </c>
       <c r="E109" t="n">
         <v>1</v>
       </c>
@@ -2304,16 +2196,15 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sandrine Benichou</t>
+          <t>Steve Elkaim</t>
         </is>
       </c>
       <c r="B110" t="n">
         <v>5</v>
       </c>
       <c r="C110" t="n">
-        <v>29</v>
-      </c>
-      <c r="D110" t="inlineStr"/>
+        <v>30</v>
+      </c>
       <c r="E110" t="n">
         <v>1</v>
       </c>
@@ -2321,16 +2212,15 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Steve Elkaim</t>
+          <t>Mari Riouallon</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C111" t="n">
-        <v>30</v>
-      </c>
-      <c r="D111" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="E111" t="n">
         <v>1</v>
       </c>
@@ -2338,7 +2228,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Mari Riouallon</t>
+          <t>Morgane Bly</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -2347,7 +2237,6 @@
       <c r="C112" t="n">
         <v>2</v>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="n">
         <v>1</v>
       </c>
@@ -2355,7 +2244,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Morgane Bly</t>
+          <t>Zaki Rochdi</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -2364,7 +2253,6 @@
       <c r="C113" t="n">
         <v>2</v>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="n">
         <v>1</v>
       </c>
@@ -2372,16 +2260,15 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Zaki Rochdi</t>
+          <t>Chaimae Zh</t>
         </is>
       </c>
       <c r="B114" t="n">
         <v>6</v>
       </c>
       <c r="C114" t="n">
-        <v>2</v>
-      </c>
-      <c r="D114" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="E114" t="n">
         <v>1</v>
       </c>
@@ -2389,16 +2276,15 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Chaimae Zh</t>
+          <t>Maelle Lafont de Sentenac</t>
         </is>
       </c>
       <c r="B115" t="n">
         <v>6</v>
       </c>
       <c r="C115" t="n">
-        <v>3</v>
-      </c>
-      <c r="D115" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="E115" t="n">
         <v>1</v>
       </c>
@@ -2406,16 +2292,15 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Maelle Lafont de Sentenac</t>
+          <t>Ai Linh DC</t>
         </is>
       </c>
       <c r="B116" t="n">
         <v>6</v>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
-      </c>
-      <c r="D116" t="inlineStr"/>
+        <v>5</v>
+      </c>
       <c r="E116" t="n">
         <v>1</v>
       </c>
@@ -2423,7 +2308,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ai Linh DC</t>
+          <t>Chloe Mateu</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -2432,7 +2317,6 @@
       <c r="C117" t="n">
         <v>5</v>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
         <v>1</v>
       </c>
@@ -2440,16 +2324,15 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Chloe Mateu</t>
+          <t>Jean Nicolini</t>
         </is>
       </c>
       <c r="B118" t="n">
         <v>6</v>
       </c>
       <c r="C118" t="n">
-        <v>5</v>
-      </c>
-      <c r="D118" t="inlineStr"/>
+        <v>6</v>
+      </c>
       <c r="E118" t="n">
         <v>1</v>
       </c>
@@ -2457,7 +2340,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Jean Nicolini</t>
+          <t>Marie Giroux</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -2466,7 +2349,6 @@
       <c r="C119" t="n">
         <v>6</v>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="n">
         <v>1</v>
       </c>
@@ -2474,16 +2356,15 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Marie Giroux</t>
+          <t>Alienor Lerouge</t>
         </is>
       </c>
       <c r="B120" t="n">
         <v>6</v>
       </c>
       <c r="C120" t="n">
-        <v>6</v>
-      </c>
-      <c r="D120" t="inlineStr"/>
+        <v>7</v>
+      </c>
       <c r="E120" t="n">
         <v>1</v>
       </c>
@@ -2491,16 +2372,15 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Alienor Lerouge</t>
+          <t>Marie-Laure Nauleau</t>
         </is>
       </c>
       <c r="B121" t="n">
         <v>6</v>
       </c>
       <c r="C121" t="n">
-        <v>7</v>
-      </c>
-      <c r="D121" t="inlineStr"/>
+        <v>8</v>
+      </c>
       <c r="E121" t="n">
         <v>1</v>
       </c>
@@ -2508,16 +2388,15 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Marie-Laure Nauleau</t>
+          <t>Fabien Piocelle</t>
         </is>
       </c>
       <c r="B122" t="n">
         <v>6</v>
       </c>
       <c r="C122" t="n">
-        <v>8</v>
-      </c>
-      <c r="D122" t="inlineStr"/>
+        <v>10</v>
+      </c>
       <c r="E122" t="n">
         <v>1</v>
       </c>
@@ -2525,16 +2404,15 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Fabien Piocelle</t>
+          <t>Aziz Temimi</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>6</v>
       </c>
       <c r="C123" t="n">
-        <v>10</v>
-      </c>
-      <c r="D123" t="inlineStr"/>
+        <v>16</v>
+      </c>
       <c r="E123" t="n">
         <v>1</v>
       </c>
@@ -2542,16 +2420,15 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Aziz Temimi</t>
+          <t>Emeric Oziel</t>
         </is>
       </c>
       <c r="B124" t="n">
         <v>6</v>
       </c>
       <c r="C124" t="n">
-        <v>16</v>
-      </c>
-      <c r="D124" t="inlineStr"/>
+        <v>18</v>
+      </c>
       <c r="E124" t="n">
         <v>1</v>
       </c>
@@ -2559,16 +2436,15 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Emeric Oziel</t>
+          <t>Greta Brunoldi</t>
         </is>
       </c>
       <c r="B125" t="n">
         <v>6</v>
       </c>
       <c r="C125" t="n">
-        <v>18</v>
-      </c>
-      <c r="D125" t="inlineStr"/>
+        <v>19</v>
+      </c>
       <c r="E125" t="n">
         <v>1</v>
       </c>
@@ -2576,16 +2452,15 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Greta Brunoldi</t>
+          <t>Alix Mja</t>
         </is>
       </c>
       <c r="B126" t="n">
         <v>6</v>
       </c>
       <c r="C126" t="n">
-        <v>19</v>
-      </c>
-      <c r="D126" t="inlineStr"/>
+        <v>20</v>
+      </c>
       <c r="E126" t="n">
         <v>1</v>
       </c>
@@ -2593,16 +2468,15 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Alix Mja</t>
+          <t>Guillaume Coudry</t>
         </is>
       </c>
       <c r="B127" t="n">
         <v>6</v>
       </c>
       <c r="C127" t="n">
-        <v>20</v>
-      </c>
-      <c r="D127" t="inlineStr"/>
+        <v>21</v>
+      </c>
       <c r="E127" t="n">
         <v>1</v>
       </c>
@@ -2610,16 +2484,15 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Guillaume Coudry</t>
+          <t>Anne Muller</t>
         </is>
       </c>
       <c r="B128" t="n">
         <v>6</v>
       </c>
       <c r="C128" t="n">
-        <v>21</v>
-      </c>
-      <c r="D128" t="inlineStr"/>
+        <v>22</v>
+      </c>
       <c r="E128" t="n">
         <v>1</v>
       </c>
@@ -2627,16 +2500,15 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Anne Muller</t>
+          <t>Flo Lcq</t>
         </is>
       </c>
       <c r="B129" t="n">
         <v>6</v>
       </c>
       <c r="C129" t="n">
-        <v>22</v>
-      </c>
-      <c r="D129" t="inlineStr"/>
+        <v>23</v>
+      </c>
       <c r="E129" t="n">
         <v>1</v>
       </c>
@@ -2644,16 +2516,15 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Flo Lcq</t>
+          <t>Dan Bkw</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>6</v>
       </c>
       <c r="C130" t="n">
-        <v>23</v>
-      </c>
-      <c r="D130" t="inlineStr"/>
+        <v>25</v>
+      </c>
       <c r="E130" t="n">
         <v>1</v>
       </c>
@@ -2661,7 +2532,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Dan Bkw</t>
+          <t>Jules Michel</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -2670,7 +2541,6 @@
       <c r="C131" t="n">
         <v>25</v>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="n">
         <v>1</v>
       </c>
@@ -2678,7 +2548,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Jules Michel</t>
+          <t>Thomas Prat</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -2687,7 +2557,6 @@
       <c r="C132" t="n">
         <v>25</v>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="n">
         <v>1</v>
       </c>
@@ -2695,16 +2564,15 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Thomas Prat</t>
+          <t>Patricia Ono</t>
         </is>
       </c>
       <c r="B133" t="n">
         <v>6</v>
       </c>
       <c r="C133" t="n">
-        <v>25</v>
-      </c>
-      <c r="D133" t="inlineStr"/>
+        <v>26</v>
+      </c>
       <c r="E133" t="n">
         <v>1</v>
       </c>
@@ -2712,16 +2580,15 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Patricia Ono</t>
+          <t>Amelie Prevost Prigent</t>
         </is>
       </c>
       <c r="B134" t="n">
         <v>6</v>
       </c>
       <c r="C134" t="n">
-        <v>26</v>
-      </c>
-      <c r="D134" t="inlineStr"/>
+        <v>27</v>
+      </c>
       <c r="E134" t="n">
         <v>1</v>
       </c>
@@ -2729,16 +2596,15 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Amelie Prevost Prigent</t>
+          <t>Julie Wirz</t>
         </is>
       </c>
       <c r="B135" t="n">
         <v>6</v>
       </c>
       <c r="C135" t="n">
-        <v>27</v>
-      </c>
-      <c r="D135" t="inlineStr"/>
+        <v>29</v>
+      </c>
       <c r="E135" t="n">
         <v>1</v>
       </c>
@@ -2746,16 +2612,15 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Julie Wirz</t>
+          <t>Celine Loriot</t>
         </is>
       </c>
       <c r="B136" t="n">
         <v>6</v>
       </c>
       <c r="C136" t="n">
-        <v>29</v>
-      </c>
-      <c r="D136" t="inlineStr"/>
+        <v>30</v>
+      </c>
       <c r="E136" t="n">
         <v>1</v>
       </c>
@@ -2763,7 +2628,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Celine Loriot</t>
+          <t>Pierre-Alexis Geoffroy</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -2772,7 +2637,6 @@
       <c r="C137" t="n">
         <v>30</v>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
         <v>1</v>
       </c>
@@ -2780,7 +2644,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Pierre-Alexis Geoffroy</t>
+          <t>Sonia Rwegera</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -2789,7 +2653,6 @@
       <c r="C138" t="n">
         <v>30</v>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="n">
         <v>1</v>
       </c>
@@ -2797,16 +2660,15 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sonia Rwegera</t>
+          <t>Barbara Conxicoeur</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C139" t="n">
-        <v>30</v>
-      </c>
-      <c r="D139" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="E139" t="n">
         <v>1</v>
       </c>
@@ -2814,7 +2676,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Barbara Conxicoeur</t>
+          <t>Erick Ebert</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -2823,7 +2685,6 @@
       <c r="C140" t="n">
         <v>2</v>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
         <v>1</v>
       </c>
@@ -2831,7 +2692,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Erick Ebert</t>
+          <t>Pauline Leriche</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -2840,7 +2701,6 @@
       <c r="C141" t="n">
         <v>2</v>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
         <v>1</v>
       </c>
@@ -2848,16 +2708,15 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Pauline Leriche</t>
+          <t>Marie-Charlotte Van de Kamp</t>
         </is>
       </c>
       <c r="B142" t="n">
         <v>7</v>
       </c>
       <c r="C142" t="n">
-        <v>2</v>
-      </c>
-      <c r="D142" t="inlineStr"/>
+        <v>5</v>
+      </c>
       <c r="E142" t="n">
         <v>1</v>
       </c>
@@ -2865,16 +2724,15 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Marie-Charlotte Van de Kamp</t>
+          <t>Aurelie Chetrit</t>
         </is>
       </c>
       <c r="B143" t="n">
         <v>7</v>
       </c>
       <c r="C143" t="n">
-        <v>5</v>
-      </c>
-      <c r="D143" t="inlineStr"/>
+        <v>9</v>
+      </c>
       <c r="E143" t="n">
         <v>1</v>
       </c>
@@ -2882,7 +2740,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Aurelie Chetrit</t>
+          <t>Pierre Ma-Kaf</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -2891,7 +2749,6 @@
       <c r="C144" t="n">
         <v>9</v>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="n">
         <v>1</v>
       </c>
@@ -2899,16 +2756,15 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Pierre Ma-Kaf</t>
+          <t>Guillaume Desloges</t>
         </is>
       </c>
       <c r="B145" t="n">
         <v>7</v>
       </c>
       <c r="C145" t="n">
-        <v>9</v>
-      </c>
-      <c r="D145" t="inlineStr"/>
+        <v>11</v>
+      </c>
       <c r="E145" t="n">
         <v>1</v>
       </c>
@@ -2916,16 +2772,15 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Guillaume Desloges</t>
+          <t>Melanie Manarin</t>
         </is>
       </c>
       <c r="B146" t="n">
         <v>7</v>
       </c>
       <c r="C146" t="n">
-        <v>11</v>
-      </c>
-      <c r="D146" t="inlineStr"/>
+        <v>12</v>
+      </c>
       <c r="E146" t="n">
         <v>1</v>
       </c>
@@ -2933,16 +2788,15 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Melanie Manarin</t>
+          <t>Jeremy Bilhant</t>
         </is>
       </c>
       <c r="B147" t="n">
         <v>7</v>
       </c>
       <c r="C147" t="n">
-        <v>12</v>
-      </c>
-      <c r="D147" t="inlineStr"/>
+        <v>14</v>
+      </c>
       <c r="E147" t="n">
         <v>1</v>
       </c>
@@ -2950,16 +2804,15 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Jeremy Bilhant</t>
+          <t>Severine Karp Tbr</t>
         </is>
       </c>
       <c r="B148" t="n">
         <v>7</v>
       </c>
       <c r="C148" t="n">
-        <v>14</v>
-      </c>
-      <c r="D148" t="inlineStr"/>
+        <v>16</v>
+      </c>
       <c r="E148" t="n">
         <v>1</v>
       </c>
@@ -2967,16 +2820,15 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Severine Karp Tbr</t>
+          <t>Paola Vllr</t>
         </is>
       </c>
       <c r="B149" t="n">
         <v>7</v>
       </c>
       <c r="C149" t="n">
-        <v>16</v>
-      </c>
-      <c r="D149" t="inlineStr"/>
+        <v>17</v>
+      </c>
       <c r="E149" t="n">
         <v>1</v>
       </c>
@@ -2984,16 +2836,15 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Paola Vllr</t>
+          <t>Come Legal</t>
         </is>
       </c>
       <c r="B150" t="n">
         <v>7</v>
       </c>
       <c r="C150" t="n">
-        <v>17</v>
-      </c>
-      <c r="D150" t="inlineStr"/>
+        <v>18</v>
+      </c>
       <c r="E150" t="n">
         <v>1</v>
       </c>
@@ -3001,16 +2852,15 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Come Legal</t>
+          <t>Melanie Mara</t>
         </is>
       </c>
       <c r="B151" t="n">
         <v>7</v>
       </c>
       <c r="C151" t="n">
-        <v>18</v>
-      </c>
-      <c r="D151" t="inlineStr"/>
+        <v>19</v>
+      </c>
       <c r="E151" t="n">
         <v>1</v>
       </c>
@@ -3018,7 +2868,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Melanie Mara</t>
+          <t>Xiayong Qin</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -3027,7 +2877,6 @@
       <c r="C152" t="n">
         <v>19</v>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="n">
         <v>1</v>
       </c>
@@ -3035,16 +2884,15 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Xiayong Qin</t>
+          <t>Dorothee Pages</t>
         </is>
       </c>
       <c r="B153" t="n">
         <v>7</v>
       </c>
       <c r="C153" t="n">
-        <v>19</v>
-      </c>
-      <c r="D153" t="inlineStr"/>
+        <v>21</v>
+      </c>
       <c r="E153" t="n">
         <v>1</v>
       </c>
@@ -3052,7 +2900,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Dorothee Pages</t>
+          <t>Elodie Mithouard</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3061,7 +2909,6 @@
       <c r="C154" t="n">
         <v>21</v>
       </c>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="n">
         <v>1</v>
       </c>
@@ -3069,16 +2916,15 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Elodie Mithouard</t>
+          <t>Vandany Asselin</t>
         </is>
       </c>
       <c r="B155" t="n">
         <v>7</v>
       </c>
       <c r="C155" t="n">
-        <v>21</v>
-      </c>
-      <c r="D155" t="inlineStr"/>
+        <v>22</v>
+      </c>
       <c r="E155" t="n">
         <v>1</v>
       </c>
@@ -3086,16 +2932,15 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Vandany Asselin</t>
+          <t>Jean-Baptiste Garnier</t>
         </is>
       </c>
       <c r="B156" t="n">
         <v>7</v>
       </c>
       <c r="C156" t="n">
-        <v>22</v>
-      </c>
-      <c r="D156" t="inlineStr"/>
+        <v>24</v>
+      </c>
       <c r="E156" t="n">
         <v>1</v>
       </c>
@@ -3103,7 +2948,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Jean-Baptiste Garnier</t>
+          <t>Lucie Forgereau</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -3112,7 +2957,6 @@
       <c r="C157" t="n">
         <v>24</v>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
         <v>1</v>
       </c>
@@ -3120,16 +2964,15 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Lucie Forgereau</t>
+          <t>David Pedrono</t>
         </is>
       </c>
       <c r="B158" t="n">
         <v>7</v>
       </c>
       <c r="C158" t="n">
-        <v>24</v>
-      </c>
-      <c r="D158" t="inlineStr"/>
+        <v>25</v>
+      </c>
       <c r="E158" t="n">
         <v>1</v>
       </c>
@@ -3137,16 +2980,15 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>David Pedrono</t>
+          <t>Hajer Gorgi</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>7</v>
       </c>
       <c r="C159" t="n">
-        <v>25</v>
-      </c>
-      <c r="D159" t="inlineStr"/>
+        <v>27</v>
+      </c>
       <c r="E159" t="n">
         <v>1</v>
       </c>
@@ -3154,16 +2996,15 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Hajer Gorgi</t>
+          <t>Gwendoline LD</t>
         </is>
       </c>
       <c r="B160" t="n">
         <v>7</v>
       </c>
       <c r="C160" t="n">
-        <v>27</v>
-      </c>
-      <c r="D160" t="inlineStr"/>
+        <v>29</v>
+      </c>
       <c r="E160" t="n">
         <v>1</v>
       </c>
@@ -3171,16 +3012,15 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Gwendoline LD</t>
+          <t>Olivier Parfait</t>
         </is>
       </c>
       <c r="B161" t="n">
         <v>7</v>
       </c>
       <c r="C161" t="n">
-        <v>29</v>
-      </c>
-      <c r="D161" t="inlineStr"/>
+        <v>30</v>
+      </c>
       <c r="E161" t="n">
         <v>1</v>
       </c>
@@ -3188,16 +3028,15 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Olivier Parfait</t>
+          <t>Antoine Tabo</t>
         </is>
       </c>
       <c r="B162" t="n">
         <v>7</v>
       </c>
       <c r="C162" t="n">
-        <v>30</v>
-      </c>
-      <c r="D162" t="inlineStr"/>
+        <v>31</v>
+      </c>
       <c r="E162" t="n">
         <v>1</v>
       </c>
@@ -3205,16 +3044,15 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Antoine Tabo</t>
+          <t>Laetitia Srt</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C163" t="n">
-        <v>31</v>
-      </c>
-      <c r="D163" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="E163" t="n">
         <v>1</v>
       </c>
@@ -3222,16 +3060,15 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Laetitia Srt</t>
+          <t>Florent Prt</t>
         </is>
       </c>
       <c r="B164" t="n">
         <v>8</v>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
-      </c>
-      <c r="D164" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="E164" t="n">
         <v>1</v>
       </c>
@@ -3239,7 +3076,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Florent Prt</t>
+          <t>Leo Leclerc</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -3248,7 +3085,6 @@
       <c r="C165" t="n">
         <v>2</v>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
         <v>1</v>
       </c>
@@ -3256,16 +3092,15 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Leo Leclerc</t>
+          <t>Caroline Lavialle</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>8</v>
       </c>
       <c r="C166" t="n">
-        <v>2</v>
-      </c>
-      <c r="D166" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="E166" t="n">
         <v>1</v>
       </c>
@@ -3273,7 +3108,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Caroline Lavialle</t>
+          <t>Jules Inadev</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -3282,7 +3117,6 @@
       <c r="C167" t="n">
         <v>3</v>
       </c>
-      <c r="D167" t="inlineStr"/>
       <c r="E167" t="n">
         <v>1</v>
       </c>
@@ -3290,7 +3124,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Jules Inadev</t>
+          <t>Julien Vedani Perso</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -3299,7 +3133,6 @@
       <c r="C168" t="n">
         <v>3</v>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="n">
         <v>1</v>
       </c>
@@ -3307,16 +3140,15 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Julien Vedani Perso</t>
+          <t>Pooja C. Thakur</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>8</v>
       </c>
       <c r="C169" t="n">
-        <v>3</v>
-      </c>
-      <c r="D169" t="inlineStr"/>
+        <v>10</v>
+      </c>
       <c r="E169" t="n">
         <v>1</v>
       </c>
@@ -3324,7 +3156,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Pooja C. Thakur</t>
+          <t>Zyad El Jebbari</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -3333,7 +3165,6 @@
       <c r="C170" t="n">
         <v>10</v>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="n">
         <v>1</v>
       </c>
@@ -3341,16 +3172,15 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Zyad El Jebbari</t>
+          <t>Fany ND</t>
         </is>
       </c>
       <c r="B171" t="n">
         <v>8</v>
       </c>
       <c r="C171" t="n">
-        <v>10</v>
-      </c>
-      <c r="D171" t="inlineStr"/>
+        <v>12</v>
+      </c>
       <c r="E171" t="n">
         <v>1</v>
       </c>
@@ -3358,7 +3188,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Fany ND</t>
+          <t>Marie-Anne Ttn</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -3367,7 +3197,6 @@
       <c r="C172" t="n">
         <v>12</v>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
         <v>1</v>
       </c>
@@ -3375,16 +3204,15 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Marie-Anne Ttn</t>
+          <t>Ellard Schutte</t>
         </is>
       </c>
       <c r="B173" t="n">
         <v>8</v>
       </c>
       <c r="C173" t="n">
-        <v>12</v>
-      </c>
-      <c r="D173" t="inlineStr"/>
+        <v>13</v>
+      </c>
       <c r="E173" t="n">
         <v>1</v>
       </c>
@@ -3392,16 +3220,15 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ellard Schutte</t>
+          <t>Ben Cottrell</t>
         </is>
       </c>
       <c r="B174" t="n">
         <v>8</v>
       </c>
       <c r="C174" t="n">
-        <v>13</v>
-      </c>
-      <c r="D174" t="inlineStr"/>
+        <v>15</v>
+      </c>
       <c r="E174" t="n">
         <v>1</v>
       </c>
@@ -3409,7 +3236,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Ben Cottrell</t>
+          <t>Pierre Roussel</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -3418,7 +3245,6 @@
       <c r="C175" t="n">
         <v>15</v>
       </c>
-      <c r="D175" t="inlineStr"/>
       <c r="E175" t="n">
         <v>1</v>
       </c>
@@ -3426,16 +3252,15 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Pierre Roussel</t>
+          <t>Dieynaba Kane</t>
         </is>
       </c>
       <c r="B176" t="n">
         <v>8</v>
       </c>
       <c r="C176" t="n">
-        <v>15</v>
-      </c>
-      <c r="D176" t="inlineStr"/>
+        <v>16</v>
+      </c>
       <c r="E176" t="n">
         <v>1</v>
       </c>
@@ -3443,16 +3268,15 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Dieynaba Kane</t>
+          <t>Alex Ldn</t>
         </is>
       </c>
       <c r="B177" t="n">
         <v>8</v>
       </c>
       <c r="C177" t="n">
-        <v>16</v>
-      </c>
-      <c r="D177" t="inlineStr"/>
+        <v>17</v>
+      </c>
       <c r="E177" t="n">
         <v>1</v>
       </c>
@@ -3460,16 +3284,15 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Alex Ldn</t>
+          <t>Thibaud Chabrelie</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>8</v>
       </c>
       <c r="C178" t="n">
-        <v>17</v>
-      </c>
-      <c r="D178" t="inlineStr"/>
+        <v>18</v>
+      </c>
       <c r="E178" t="n">
         <v>1</v>
       </c>
@@ -3477,16 +3300,15 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Thibaud Chabrelie</t>
+          <t>Caro Sibaud</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>8</v>
       </c>
       <c r="C179" t="n">
-        <v>18</v>
-      </c>
-      <c r="D179" t="inlineStr"/>
+        <v>21</v>
+      </c>
       <c r="E179" t="n">
         <v>1</v>
       </c>
@@ -3494,7 +3316,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Caro Sibaud</t>
+          <t>Othmane Ouali</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -3503,7 +3325,6 @@
       <c r="C180" t="n">
         <v>21</v>
       </c>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
         <v>1</v>
       </c>
@@ -3511,7 +3332,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Othmane Ouali</t>
+          <t>Xavier V-n</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -3520,7 +3341,6 @@
       <c r="C181" t="n">
         <v>21</v>
       </c>
-      <c r="D181" t="inlineStr"/>
       <c r="E181" t="n">
         <v>1</v>
       </c>
@@ -3528,16 +3348,15 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Xavier V-n</t>
+          <t>Maroua BenJamaa</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>8</v>
       </c>
       <c r="C182" t="n">
-        <v>21</v>
-      </c>
-      <c r="D182" t="inlineStr"/>
+        <v>23</v>
+      </c>
       <c r="E182" t="n">
         <v>1</v>
       </c>
@@ -3545,16 +3364,15 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Maroua BenJamaa</t>
+          <t>Thomas Mnzl</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>8</v>
       </c>
       <c r="C183" t="n">
-        <v>23</v>
-      </c>
-      <c r="D183" t="inlineStr"/>
+        <v>25</v>
+      </c>
       <c r="E183" t="n">
         <v>1</v>
       </c>
@@ -3562,16 +3380,15 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Thomas Mnzl</t>
+          <t>Cedric Sap</t>
         </is>
       </c>
       <c r="B184" t="n">
         <v>8</v>
       </c>
       <c r="C184" t="n">
-        <v>25</v>
-      </c>
-      <c r="D184" t="inlineStr"/>
+        <v>26</v>
+      </c>
       <c r="E184" t="n">
         <v>1</v>
       </c>
@@ -3579,16 +3396,15 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Cedric Sap</t>
+          <t>Justine Deschamps</t>
         </is>
       </c>
       <c r="B185" t="n">
         <v>8</v>
       </c>
       <c r="C185" t="n">
-        <v>26</v>
-      </c>
-      <c r="D185" t="inlineStr"/>
+        <v>28</v>
+      </c>
       <c r="E185" t="n">
         <v>1</v>
       </c>
@@ -3596,7 +3412,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Justine Deschamps</t>
+          <t>Lili Jolie</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -3605,7 +3421,6 @@
       <c r="C186" t="n">
         <v>28</v>
       </c>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="n">
         <v>1</v>
       </c>
@@ -3613,7 +3428,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Lili Jolie</t>
+          <t>Pierre Guti</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -3622,7 +3437,6 @@
       <c r="C187" t="n">
         <v>28</v>
       </c>
-      <c r="D187" t="inlineStr"/>
       <c r="E187" t="n">
         <v>1</v>
       </c>
@@ -3630,16 +3444,15 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Pierre Guti</t>
+          <t>Saïd Abbou</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>8</v>
       </c>
       <c r="C188" t="n">
-        <v>28</v>
-      </c>
-      <c r="D188" t="inlineStr"/>
+        <v>29</v>
+      </c>
       <c r="E188" t="n">
         <v>1</v>
       </c>
@@ -3647,16 +3460,15 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Saïd Abbou</t>
+          <t>Mathieu Llrn</t>
         </is>
       </c>
       <c r="B189" t="n">
         <v>8</v>
       </c>
       <c r="C189" t="n">
-        <v>29</v>
-      </c>
-      <c r="D189" t="inlineStr"/>
+        <v>30</v>
+      </c>
       <c r="E189" t="n">
         <v>1</v>
       </c>
@@ -3664,7 +3476,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Mathieu Llrn</t>
+          <t>Pierre-Edouard Arrouy</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -3673,7 +3485,6 @@
       <c r="C190" t="n">
         <v>30</v>
       </c>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="n">
         <v>1</v>
       </c>
@@ -3681,16 +3492,15 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Pierre-Edouard Arrouy</t>
+          <t>Christophe Bnf</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C191" t="n">
-        <v>30</v>
-      </c>
-      <c r="D191" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="E191" t="n">
         <v>1</v>
       </c>
@@ -3698,7 +3508,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Christophe Bnf</t>
+          <t>Imane Aitlachgar</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -3707,7 +3517,6 @@
       <c r="C192" t="n">
         <v>1</v>
       </c>
-      <c r="D192" t="inlineStr"/>
       <c r="E192" t="n">
         <v>1</v>
       </c>
@@ -3715,16 +3524,15 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Imane Aitlachgar</t>
+          <t>Laurie Simo</t>
         </is>
       </c>
       <c r="B193" t="n">
         <v>9</v>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
-      </c>
-      <c r="D193" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="E193" t="n">
         <v>1</v>
       </c>
@@ -3732,16 +3540,15 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Laurie Simo</t>
+          <t>Julie Colomb</t>
         </is>
       </c>
       <c r="B194" t="n">
         <v>9</v>
       </c>
       <c r="C194" t="n">
-        <v>2</v>
-      </c>
-      <c r="D194" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="E194" t="n">
         <v>1</v>
       </c>
@@ -3749,16 +3556,15 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Julie Colomb</t>
+          <t>Emilie LE</t>
         </is>
       </c>
       <c r="B195" t="n">
         <v>9</v>
       </c>
       <c r="C195" t="n">
-        <v>3</v>
-      </c>
-      <c r="D195" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="E195" t="n">
         <v>1</v>
       </c>
@@ -3766,7 +3572,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Emilie LE</t>
+          <t>Laure Gio</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -3775,7 +3581,6 @@
       <c r="C196" t="n">
         <v>4</v>
       </c>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" t="n">
         <v>1</v>
       </c>
@@ -3783,7 +3588,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Laure Gio</t>
+          <t>Pierre Daher</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -3792,7 +3597,6 @@
       <c r="C197" t="n">
         <v>4</v>
       </c>
-      <c r="D197" t="inlineStr"/>
       <c r="E197" t="n">
         <v>1</v>
       </c>
@@ -3800,16 +3604,15 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Pierre Daher</t>
+          <t>Audrey Cg</t>
         </is>
       </c>
       <c r="B198" t="n">
         <v>9</v>
       </c>
       <c r="C198" t="n">
-        <v>4</v>
-      </c>
-      <c r="D198" t="inlineStr"/>
+        <v>5</v>
+      </c>
       <c r="E198" t="n">
         <v>1</v>
       </c>
@@ -3817,7 +3620,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Audrey Cg</t>
+          <t>Delph LeMeur</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -3826,7 +3629,6 @@
       <c r="C199" t="n">
         <v>5</v>
       </c>
-      <c r="D199" t="inlineStr"/>
       <c r="E199" t="n">
         <v>1</v>
       </c>
@@ -3834,7 +3636,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Delph LeMeur</t>
+          <t>Gaelle Mione</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -3843,7 +3645,6 @@
       <c r="C200" t="n">
         <v>5</v>
       </c>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" t="n">
         <v>1</v>
       </c>
@@ -3851,16 +3652,15 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Gaelle Mione</t>
+          <t>Nora Brauch</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>9</v>
       </c>
       <c r="C201" t="n">
-        <v>5</v>
-      </c>
-      <c r="D201" t="inlineStr"/>
+        <v>7</v>
+      </c>
       <c r="E201" t="n">
         <v>1</v>
       </c>
@@ -3868,7 +3668,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Nora Brauch</t>
+          <t>Roman Rsx</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -3877,7 +3677,6 @@
       <c r="C202" t="n">
         <v>7</v>
       </c>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" t="n">
         <v>1</v>
       </c>
@@ -3885,16 +3684,15 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Roman Rsx</t>
+          <t>Mathilde Lebrand</t>
         </is>
       </c>
       <c r="B203" t="n">
         <v>9</v>
       </c>
       <c r="C203" t="n">
-        <v>7</v>
-      </c>
-      <c r="D203" t="inlineStr"/>
+        <v>9</v>
+      </c>
       <c r="E203" t="n">
         <v>1</v>
       </c>
@@ -3902,16 +3700,15 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Mathilde Lebrand</t>
+          <t>Barbie Shrack</t>
         </is>
       </c>
       <c r="B204" t="n">
         <v>9</v>
       </c>
       <c r="C204" t="n">
-        <v>9</v>
-      </c>
-      <c r="D204" t="inlineStr"/>
+        <v>11</v>
+      </c>
       <c r="E204" t="n">
         <v>1</v>
       </c>
@@ -3919,7 +3716,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Barbie Shrack</t>
+          <t>Jacky Cohen</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -3928,7 +3725,6 @@
       <c r="C205" t="n">
         <v>11</v>
       </c>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" t="n">
         <v>1</v>
       </c>
@@ -3936,16 +3732,15 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Jacky Cohen</t>
+          <t>Julien Galzy</t>
         </is>
       </c>
       <c r="B206" t="n">
         <v>9</v>
       </c>
       <c r="C206" t="n">
-        <v>11</v>
-      </c>
-      <c r="D206" t="inlineStr"/>
+        <v>13</v>
+      </c>
       <c r="E206" t="n">
         <v>1</v>
       </c>
@@ -3953,16 +3748,15 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Julien Galzy</t>
+          <t>Laety Cia</t>
         </is>
       </c>
       <c r="B207" t="n">
         <v>9</v>
       </c>
       <c r="C207" t="n">
-        <v>13</v>
-      </c>
-      <c r="D207" t="inlineStr"/>
+        <v>17</v>
+      </c>
       <c r="E207" t="n">
         <v>1</v>
       </c>
@@ -3970,7 +3764,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Laety Cia</t>
+          <t>Laetitia Oziel</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -3979,7 +3773,6 @@
       <c r="C208" t="n">
         <v>17</v>
       </c>
-      <c r="D208" t="inlineStr"/>
       <c r="E208" t="n">
         <v>1</v>
       </c>
@@ -3987,16 +3780,15 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Laetitia Oziel</t>
+          <t>Nicolas Cerrajero</t>
         </is>
       </c>
       <c r="B209" t="n">
         <v>9</v>
       </c>
       <c r="C209" t="n">
-        <v>17</v>
-      </c>
-      <c r="D209" t="inlineStr"/>
+        <v>21</v>
+      </c>
       <c r="E209" t="n">
         <v>1</v>
       </c>
@@ -4004,16 +3796,15 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Nicolas Cerrajero</t>
+          <t>Anandan Lamartine</t>
         </is>
       </c>
       <c r="B210" t="n">
         <v>9</v>
       </c>
       <c r="C210" t="n">
-        <v>21</v>
-      </c>
-      <c r="D210" t="inlineStr"/>
+        <v>24</v>
+      </c>
       <c r="E210" t="n">
         <v>1</v>
       </c>
@@ -4021,7 +3812,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Anandan Lamartine</t>
+          <t>Constance Ayoub</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -4030,7 +3821,6 @@
       <c r="C211" t="n">
         <v>24</v>
       </c>
-      <c r="D211" t="inlineStr"/>
       <c r="E211" t="n">
         <v>1</v>
       </c>
@@ -4038,16 +3828,15 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Constance Ayoub</t>
+          <t>Marion Chandes</t>
         </is>
       </c>
       <c r="B212" t="n">
         <v>9</v>
       </c>
       <c r="C212" t="n">
-        <v>24</v>
-      </c>
-      <c r="D212" t="inlineStr"/>
+        <v>25</v>
+      </c>
       <c r="E212" t="n">
         <v>1</v>
       </c>
@@ -4055,16 +3844,15 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Marion Chandes</t>
+          <t>Emilie Protin</t>
         </is>
       </c>
       <c r="B213" t="n">
         <v>9</v>
       </c>
       <c r="C213" t="n">
-        <v>25</v>
-      </c>
-      <c r="D213" t="inlineStr"/>
+        <v>27</v>
+      </c>
       <c r="E213" t="n">
         <v>1</v>
       </c>
@@ -4072,16 +3860,15 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Emilie Protin</t>
+          <t>Tiphaine Perache</t>
         </is>
       </c>
       <c r="B214" t="n">
         <v>9</v>
       </c>
       <c r="C214" t="n">
-        <v>27</v>
-      </c>
-      <c r="D214" t="inlineStr"/>
+        <v>29</v>
+      </c>
       <c r="E214" t="n">
         <v>1</v>
       </c>
@@ -4089,16 +3876,15 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Tiphaine Perache</t>
+          <t>Alban Marsoin</t>
         </is>
       </c>
       <c r="B215" t="n">
         <v>9</v>
       </c>
       <c r="C215" t="n">
-        <v>29</v>
-      </c>
-      <c r="D215" t="inlineStr"/>
+        <v>30</v>
+      </c>
       <c r="E215" t="n">
         <v>1</v>
       </c>
@@ -4106,16 +3892,15 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Alban Marsoin</t>
+          <t>Cceline Lanchas</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C216" t="n">
-        <v>30</v>
-      </c>
-      <c r="D216" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="E216" t="n">
         <v>1</v>
       </c>
@@ -4123,16 +3908,15 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Cceline Lanchas</t>
+          <t>Alexandre Collin</t>
         </is>
       </c>
       <c r="B217" t="n">
         <v>10</v>
       </c>
       <c r="C217" t="n">
-        <v>1</v>
-      </c>
-      <c r="D217" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="E217" t="n">
         <v>1</v>
       </c>
@@ -4140,7 +3924,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Alexandre Collin</t>
+          <t>Pol Besse</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -4149,7 +3933,6 @@
       <c r="C218" t="n">
         <v>2</v>
       </c>
-      <c r="D218" t="inlineStr"/>
       <c r="E218" t="n">
         <v>1</v>
       </c>
@@ -4157,16 +3940,15 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Pol Besse</t>
+          <t>Juliet Aloha</t>
         </is>
       </c>
       <c r="B219" t="n">
         <v>10</v>
       </c>
       <c r="C219" t="n">
-        <v>2</v>
-      </c>
-      <c r="D219" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="E219" t="n">
         <v>1</v>
       </c>
@@ -4174,7 +3956,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Juliet Aloha</t>
+          <t>Thierry Plesnar Dennås</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -4183,7 +3965,6 @@
       <c r="C220" t="n">
         <v>3</v>
       </c>
-      <c r="D220" t="inlineStr"/>
       <c r="E220" t="n">
         <v>1</v>
       </c>
@@ -4191,16 +3972,15 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Thierry Plesnar Dennås</t>
+          <t>Heloïse Beaufils</t>
         </is>
       </c>
       <c r="B221" t="n">
         <v>10</v>
       </c>
       <c r="C221" t="n">
-        <v>3</v>
-      </c>
-      <c r="D221" t="inlineStr"/>
+        <v>5</v>
+      </c>
       <c r="E221" t="n">
         <v>1</v>
       </c>
@@ -4208,16 +3988,15 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Heloïse Beaufils</t>
+          <t>Aymeric Lanquetot</t>
         </is>
       </c>
       <c r="B222" t="n">
         <v>10</v>
       </c>
       <c r="C222" t="n">
-        <v>5</v>
-      </c>
-      <c r="D222" t="inlineStr"/>
+        <v>6</v>
+      </c>
       <c r="E222" t="n">
         <v>1</v>
       </c>
@@ -4225,7 +4004,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Aymeric Lanquetot</t>
+          <t>Laurene Depp</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -4234,7 +4013,6 @@
       <c r="C223" t="n">
         <v>6</v>
       </c>
-      <c r="D223" t="inlineStr"/>
       <c r="E223" t="n">
         <v>1</v>
       </c>
@@ -4242,16 +4020,15 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Laurene Depp</t>
+          <t>Augustin Wirz</t>
         </is>
       </c>
       <c r="B224" t="n">
         <v>10</v>
       </c>
       <c r="C224" t="n">
-        <v>6</v>
-      </c>
-      <c r="D224" t="inlineStr"/>
+        <v>7</v>
+      </c>
       <c r="E224" t="n">
         <v>1</v>
       </c>
@@ -4259,16 +4036,15 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Augustin Wirz</t>
+          <t>Berangere Montamat-Dubs Iad France</t>
         </is>
       </c>
       <c r="B225" t="n">
         <v>10</v>
       </c>
       <c r="C225" t="n">
-        <v>7</v>
-      </c>
-      <c r="D225" t="inlineStr"/>
+        <v>9</v>
+      </c>
       <c r="E225" t="n">
         <v>1</v>
       </c>
@@ -4276,7 +4052,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Berangere Montamat-Dubs Iad France</t>
+          <t>Berangere Mtsbud</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -4285,7 +4061,6 @@
       <c r="C226" t="n">
         <v>9</v>
       </c>
-      <c r="D226" t="inlineStr"/>
       <c r="E226" t="n">
         <v>1</v>
       </c>
@@ -4293,7 +4068,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Berangere Mtsbud</t>
+          <t>David De Cress</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -4302,7 +4077,6 @@
       <c r="C227" t="n">
         <v>9</v>
       </c>
-      <c r="D227" t="inlineStr"/>
       <c r="E227" t="n">
         <v>1</v>
       </c>
@@ -4310,7 +4084,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>David De Cress</t>
+          <t>Paul Mithouard</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -4319,7 +4093,6 @@
       <c r="C228" t="n">
         <v>9</v>
       </c>
-      <c r="D228" t="inlineStr"/>
       <c r="E228" t="n">
         <v>1</v>
       </c>
@@ -4327,7 +4100,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Paul Mithouard</t>
+          <t>Stephane Hal</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -4336,7 +4109,6 @@
       <c r="C229" t="n">
         <v>9</v>
       </c>
-      <c r="D229" t="inlineStr"/>
       <c r="E229" t="n">
         <v>1</v>
       </c>
@@ -4344,16 +4116,15 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Stephane Hal</t>
+          <t>Thomas Dickele</t>
         </is>
       </c>
       <c r="B230" t="n">
         <v>10</v>
       </c>
       <c r="C230" t="n">
-        <v>9</v>
-      </c>
-      <c r="D230" t="inlineStr"/>
+        <v>10</v>
+      </c>
       <c r="E230" t="n">
         <v>1</v>
       </c>
@@ -4361,16 +4132,15 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Thomas Dickele</t>
+          <t>Tony Heng</t>
         </is>
       </c>
       <c r="B231" t="n">
         <v>10</v>
       </c>
       <c r="C231" t="n">
-        <v>10</v>
-      </c>
-      <c r="D231" t="inlineStr"/>
+        <v>12</v>
+      </c>
       <c r="E231" t="n">
         <v>1</v>
       </c>
@@ -4378,16 +4148,15 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Tony Heng</t>
+          <t>Mary Duckham</t>
         </is>
       </c>
       <c r="B232" t="n">
         <v>10</v>
       </c>
       <c r="C232" t="n">
-        <v>12</v>
-      </c>
-      <c r="D232" t="inlineStr"/>
+        <v>13</v>
+      </c>
       <c r="E232" t="n">
         <v>1</v>
       </c>
@@ -4395,7 +4164,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Mary Duckham</t>
+          <t>Quentin Grandjean</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -4404,7 +4173,6 @@
       <c r="C233" t="n">
         <v>13</v>
       </c>
-      <c r="D233" t="inlineStr"/>
       <c r="E233" t="n">
         <v>1</v>
       </c>
@@ -4412,16 +4180,15 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Quentin Grandjean</t>
+          <t>Kenji Kanazawa</t>
         </is>
       </c>
       <c r="B234" t="n">
         <v>10</v>
       </c>
       <c r="C234" t="n">
-        <v>13</v>
-      </c>
-      <c r="D234" t="inlineStr"/>
+        <v>14</v>
+      </c>
       <c r="E234" t="n">
         <v>1</v>
       </c>
@@ -4429,16 +4196,15 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Kenji Kanazawa</t>
+          <t>Alexis Toujas</t>
         </is>
       </c>
       <c r="B235" t="n">
         <v>10</v>
       </c>
       <c r="C235" t="n">
-        <v>14</v>
-      </c>
-      <c r="D235" t="inlineStr"/>
+        <v>22</v>
+      </c>
       <c r="E235" t="n">
         <v>1</v>
       </c>
@@ -4446,16 +4212,15 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Alexis Toujas</t>
+          <t>Caroline Ebert</t>
         </is>
       </c>
       <c r="B236" t="n">
         <v>10</v>
       </c>
       <c r="C236" t="n">
-        <v>22</v>
-      </c>
-      <c r="D236" t="inlineStr"/>
+        <v>24</v>
+      </c>
       <c r="E236" t="n">
         <v>1</v>
       </c>
@@ -4463,7 +4228,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Caroline Ebert</t>
+          <t>Samy Collier</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -4472,7 +4237,6 @@
       <c r="C237" t="n">
         <v>24</v>
       </c>
-      <c r="D237" t="inlineStr"/>
       <c r="E237" t="n">
         <v>1</v>
       </c>
@@ -4480,16 +4244,15 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Samy Collier</t>
+          <t>Claire Boutreux</t>
         </is>
       </c>
       <c r="B238" t="n">
         <v>10</v>
       </c>
       <c r="C238" t="n">
-        <v>24</v>
-      </c>
-      <c r="D238" t="inlineStr"/>
+        <v>26</v>
+      </c>
       <c r="E238" t="n">
         <v>1</v>
       </c>
@@ -4497,7 +4260,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Claire Boutreux</t>
+          <t>Marie Coleman</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -4506,7 +4269,6 @@
       <c r="C239" t="n">
         <v>26</v>
       </c>
-      <c r="D239" t="inlineStr"/>
       <c r="E239" t="n">
         <v>1</v>
       </c>
@@ -4514,7 +4276,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Marie Coleman</t>
+          <t>Zhibin Cai</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -4523,7 +4285,6 @@
       <c r="C240" t="n">
         <v>26</v>
       </c>
-      <c r="D240" t="inlineStr"/>
       <c r="E240" t="n">
         <v>1</v>
       </c>
@@ -4531,16 +4292,15 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Zhibin Cai</t>
+          <t>Charlotte Perinelli</t>
         </is>
       </c>
       <c r="B241" t="n">
         <v>10</v>
       </c>
       <c r="C241" t="n">
-        <v>26</v>
-      </c>
-      <c r="D241" t="inlineStr"/>
+        <v>27</v>
+      </c>
       <c r="E241" t="n">
         <v>1</v>
       </c>
@@ -4548,16 +4308,15 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Charlotte Perinelli</t>
+          <t>Pierre-Hugues Gille</t>
         </is>
       </c>
       <c r="B242" t="n">
         <v>10</v>
       </c>
       <c r="C242" t="n">
-        <v>27</v>
-      </c>
-      <c r="D242" t="inlineStr"/>
+        <v>28</v>
+      </c>
       <c r="E242" t="n">
         <v>1</v>
       </c>
@@ -4565,16 +4324,15 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Pierre-Hugues Gille</t>
+          <t>Brigit Bip</t>
         </is>
       </c>
       <c r="B243" t="n">
         <v>10</v>
       </c>
       <c r="C243" t="n">
-        <v>28</v>
-      </c>
-      <c r="D243" t="inlineStr"/>
+        <v>29</v>
+      </c>
       <c r="E243" t="n">
         <v>1</v>
       </c>
@@ -4582,16 +4340,15 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Brigit Bip</t>
+          <t>Emmanuel Av</t>
         </is>
       </c>
       <c r="B244" t="n">
         <v>10</v>
       </c>
       <c r="C244" t="n">
-        <v>29</v>
-      </c>
-      <c r="D244" t="inlineStr"/>
+        <v>31</v>
+      </c>
       <c r="E244" t="n">
         <v>1</v>
       </c>
@@ -4599,7 +4356,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Emmanuel Av</t>
+          <t>Martin Grv</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -4608,7 +4365,6 @@
       <c r="C245" t="n">
         <v>31</v>
       </c>
-      <c r="D245" t="inlineStr"/>
       <c r="E245" t="n">
         <v>1</v>
       </c>
@@ -4616,16 +4372,15 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Martin Grv</t>
+          <t>Oussema Trigui</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C246" t="n">
-        <v>31</v>
-      </c>
-      <c r="D246" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="E246" t="n">
         <v>1</v>
       </c>
@@ -4633,16 +4388,15 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Oussema Trigui</t>
+          <t>Ahmed AR</t>
         </is>
       </c>
       <c r="B247" t="n">
         <v>11</v>
       </c>
       <c r="C247" t="n">
-        <v>1</v>
-      </c>
-      <c r="D247" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="E247" t="n">
         <v>1</v>
       </c>
@@ -4650,7 +4404,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Ahmed AR</t>
+          <t>Younes Tahiri</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -4659,7 +4413,6 @@
       <c r="C248" t="n">
         <v>2</v>
       </c>
-      <c r="D248" t="inlineStr"/>
       <c r="E248" t="n">
         <v>1</v>
       </c>
@@ -4667,16 +4420,15 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Younes Tahiri</t>
+          <t>Daphne Cunnington</t>
         </is>
       </c>
       <c r="B249" t="n">
         <v>11</v>
       </c>
       <c r="C249" t="n">
-        <v>2</v>
-      </c>
-      <c r="D249" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="E249" t="n">
         <v>1</v>
       </c>
@@ -4684,16 +4436,15 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Daphne Cunnington</t>
+          <t>Francois Lab Lamberdiere Sle</t>
         </is>
       </c>
       <c r="B250" t="n">
         <v>11</v>
       </c>
       <c r="C250" t="n">
-        <v>3</v>
-      </c>
-      <c r="D250" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="E250" t="n">
         <v>1</v>
       </c>
@@ -4701,16 +4452,15 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Francois Lab Lamberdiere Sle</t>
+          <t>Gaetan Guillotin</t>
         </is>
       </c>
       <c r="B251" t="n">
         <v>11</v>
       </c>
       <c r="C251" t="n">
-        <v>4</v>
-      </c>
-      <c r="D251" t="inlineStr"/>
+        <v>6</v>
+      </c>
       <c r="E251" t="n">
         <v>1</v>
       </c>
@@ -4718,7 +4468,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Gaetan Guillotin</t>
+          <t>Sarah Colin</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -4727,7 +4477,6 @@
       <c r="C252" t="n">
         <v>6</v>
       </c>
-      <c r="D252" t="inlineStr"/>
       <c r="E252" t="n">
         <v>1</v>
       </c>
@@ -4735,16 +4484,15 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Sarah Colin</t>
+          <t>Yoann Bld</t>
         </is>
       </c>
       <c r="B253" t="n">
         <v>11</v>
       </c>
       <c r="C253" t="n">
-        <v>6</v>
-      </c>
-      <c r="D253" t="inlineStr"/>
+        <v>7</v>
+      </c>
       <c r="E253" t="n">
         <v>1</v>
       </c>
@@ -4752,16 +4500,15 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Yoann Bld</t>
+          <t>Fabrice Galea</t>
         </is>
       </c>
       <c r="B254" t="n">
         <v>11</v>
       </c>
       <c r="C254" t="n">
-        <v>7</v>
-      </c>
-      <c r="D254" t="inlineStr"/>
+        <v>9</v>
+      </c>
       <c r="E254" t="n">
         <v>1</v>
       </c>
@@ -4769,7 +4516,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Fabrice Galea</t>
+          <t>Melodie Baudusseau</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -4778,7 +4525,6 @@
       <c r="C255" t="n">
         <v>9</v>
       </c>
-      <c r="D255" t="inlineStr"/>
       <c r="E255" t="n">
         <v>1</v>
       </c>
@@ -4786,16 +4532,15 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Melodie Baudusseau</t>
+          <t>Guillaume Zeganadin</t>
         </is>
       </c>
       <c r="B256" t="n">
         <v>11</v>
       </c>
       <c r="C256" t="n">
-        <v>9</v>
-      </c>
-      <c r="D256" t="inlineStr"/>
+        <v>10</v>
+      </c>
       <c r="E256" t="n">
         <v>1</v>
       </c>
@@ -4803,7 +4548,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Guillaume Zeganadin</t>
+          <t>Marion Pelata</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -4812,7 +4557,6 @@
       <c r="C257" t="n">
         <v>10</v>
       </c>
-      <c r="D257" t="inlineStr"/>
       <c r="E257" t="n">
         <v>1</v>
       </c>
@@ -4820,7 +4564,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Marion Pelata</t>
+          <t>Pauline Lorraine</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -4829,7 +4573,6 @@
       <c r="C258" t="n">
         <v>10</v>
       </c>
-      <c r="D258" t="inlineStr"/>
       <c r="E258" t="n">
         <v>1</v>
       </c>
@@ -4837,16 +4580,15 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Pauline Lorraine</t>
+          <t>Axelle Schwob</t>
         </is>
       </c>
       <c r="B259" t="n">
         <v>11</v>
       </c>
       <c r="C259" t="n">
-        <v>10</v>
-      </c>
-      <c r="D259" t="inlineStr"/>
+        <v>12</v>
+      </c>
       <c r="E259" t="n">
         <v>1</v>
       </c>
@@ -4854,7 +4596,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Axelle Schwob</t>
+          <t>Clemence Dupont</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -4863,7 +4605,6 @@
       <c r="C260" t="n">
         <v>12</v>
       </c>
-      <c r="D260" t="inlineStr"/>
       <c r="E260" t="n">
         <v>1</v>
       </c>
@@ -4871,7 +4612,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Clemence Dupont</t>
+          <t>Marion Dup Lec</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -4880,7 +4621,6 @@
       <c r="C261" t="n">
         <v>12</v>
       </c>
-      <c r="D261" t="inlineStr"/>
       <c r="E261" t="n">
         <v>1</v>
       </c>
@@ -4888,16 +4628,15 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Marion Dup Lec</t>
+          <t>Jeremy Rousset</t>
         </is>
       </c>
       <c r="B262" t="n">
         <v>11</v>
       </c>
       <c r="C262" t="n">
-        <v>12</v>
-      </c>
-      <c r="D262" t="inlineStr"/>
+        <v>13</v>
+      </c>
       <c r="E262" t="n">
         <v>1</v>
       </c>
@@ -4905,7 +4644,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Jeremy Rousset</t>
+          <t>Mickael Rauch</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -4914,7 +4653,6 @@
       <c r="C263" t="n">
         <v>13</v>
       </c>
-      <c r="D263" t="inlineStr"/>
       <c r="E263" t="n">
         <v>1</v>
       </c>
@@ -4922,16 +4660,15 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Mickael Rauch</t>
+          <t>Xavier Montamat</t>
         </is>
       </c>
       <c r="B264" t="n">
         <v>11</v>
       </c>
       <c r="C264" t="n">
-        <v>13</v>
-      </c>
-      <c r="D264" t="inlineStr"/>
+        <v>14</v>
+      </c>
       <c r="E264" t="n">
         <v>1</v>
       </c>
@@ -4939,16 +4676,15 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Xavier Montamat</t>
+          <t>Adrien Vila</t>
         </is>
       </c>
       <c r="B265" t="n">
         <v>11</v>
       </c>
       <c r="C265" t="n">
-        <v>14</v>
-      </c>
-      <c r="D265" t="inlineStr"/>
+        <v>15</v>
+      </c>
       <c r="E265" t="n">
         <v>1</v>
       </c>
@@ -4956,16 +4692,15 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Adrien Vila</t>
+          <t>Diane Catala</t>
         </is>
       </c>
       <c r="B266" t="n">
         <v>11</v>
       </c>
       <c r="C266" t="n">
-        <v>15</v>
-      </c>
-      <c r="D266" t="inlineStr"/>
+        <v>17</v>
+      </c>
       <c r="E266" t="n">
         <v>1</v>
       </c>
@@ -4973,7 +4708,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Diane Catala</t>
+          <t>Kevin Tracol</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -4982,7 +4717,6 @@
       <c r="C267" t="n">
         <v>17</v>
       </c>
-      <c r="D267" t="inlineStr"/>
       <c r="E267" t="n">
         <v>1</v>
       </c>
@@ -4990,16 +4724,15 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Kevin Tracol</t>
+          <t>Sophie Reeves</t>
         </is>
       </c>
       <c r="B268" t="n">
         <v>11</v>
       </c>
       <c r="C268" t="n">
-        <v>17</v>
-      </c>
-      <c r="D268" t="inlineStr"/>
+        <v>18</v>
+      </c>
       <c r="E268" t="n">
         <v>1</v>
       </c>
@@ -5007,16 +4740,15 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Sophie Reeves</t>
+          <t>Fritz Pierre</t>
         </is>
       </c>
       <c r="B269" t="n">
         <v>11</v>
       </c>
       <c r="C269" t="n">
-        <v>18</v>
-      </c>
-      <c r="D269" t="inlineStr"/>
+        <v>22</v>
+      </c>
       <c r="E269" t="n">
         <v>1</v>
       </c>
@@ -5024,16 +4756,15 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Fritz Pierre</t>
+          <t>Chana Lzm</t>
         </is>
       </c>
       <c r="B270" t="n">
         <v>11</v>
       </c>
       <c r="C270" t="n">
-        <v>22</v>
-      </c>
-      <c r="D270" t="inlineStr"/>
+        <v>23</v>
+      </c>
       <c r="E270" t="n">
         <v>1</v>
       </c>
@@ -5041,16 +4772,15 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Chana Lzm</t>
+          <t>Alexandre Assaïr</t>
         </is>
       </c>
       <c r="B271" t="n">
         <v>11</v>
       </c>
       <c r="C271" t="n">
-        <v>23</v>
-      </c>
-      <c r="D271" t="inlineStr"/>
+        <v>24</v>
+      </c>
       <c r="E271" t="n">
         <v>1</v>
       </c>
@@ -5058,7 +4788,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Alexandre Assaïr</t>
+          <t>Florian Capolunghi</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -5067,7 +4797,6 @@
       <c r="C272" t="n">
         <v>24</v>
       </c>
-      <c r="D272" t="inlineStr"/>
       <c r="E272" t="n">
         <v>1</v>
       </c>
@@ -5075,16 +4804,15 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Florian Capolunghi</t>
+          <t>Arnaud Chape</t>
         </is>
       </c>
       <c r="B273" t="n">
         <v>11</v>
       </c>
       <c r="C273" t="n">
-        <v>24</v>
-      </c>
-      <c r="D273" t="inlineStr"/>
+        <v>25</v>
+      </c>
       <c r="E273" t="n">
         <v>1</v>
       </c>
@@ -5092,7 +4820,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Arnaud Chape</t>
+          <t>Elie Murard</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -5101,7 +4829,6 @@
       <c r="C274" t="n">
         <v>25</v>
       </c>
-      <c r="D274" t="inlineStr"/>
       <c r="E274" t="n">
         <v>1</v>
       </c>
@@ -5109,7 +4836,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Elie Murard</t>
+          <t>Marian Petitfils</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -5118,7 +4845,6 @@
       <c r="C275" t="n">
         <v>25</v>
       </c>
-      <c r="D275" t="inlineStr"/>
       <c r="E275" t="n">
         <v>1</v>
       </c>
@@ -5126,16 +4852,15 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Marian Petitfils</t>
+          <t>Lamia Cacciaguerra Mahdjoub</t>
         </is>
       </c>
       <c r="B276" t="n">
         <v>11</v>
       </c>
       <c r="C276" t="n">
-        <v>25</v>
-      </c>
-      <c r="D276" t="inlineStr"/>
+        <v>27</v>
+      </c>
       <c r="E276" t="n">
         <v>1</v>
       </c>
@@ -5143,16 +4868,15 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Lamia Cacciaguerra Mahdjoub</t>
+          <t>Long Do Cao</t>
         </is>
       </c>
       <c r="B277" t="n">
         <v>11</v>
       </c>
       <c r="C277" t="n">
-        <v>27</v>
-      </c>
-      <c r="D277" t="inlineStr"/>
+        <v>28</v>
+      </c>
       <c r="E277" t="n">
         <v>1</v>
       </c>
@@ -5160,7 +4884,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Long Do Cao</t>
+          <t>Sarah Valentine</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -5169,7 +4893,6 @@
       <c r="C278" t="n">
         <v>28</v>
       </c>
-      <c r="D278" t="inlineStr"/>
       <c r="E278" t="n">
         <v>1</v>
       </c>
@@ -5177,16 +4900,15 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Sarah Valentine</t>
+          <t>Antoine Rodriguez</t>
         </is>
       </c>
       <c r="B279" t="n">
         <v>11</v>
       </c>
       <c r="C279" t="n">
-        <v>28</v>
-      </c>
-      <c r="D279" t="inlineStr"/>
+        <v>29</v>
+      </c>
       <c r="E279" t="n">
         <v>1</v>
       </c>
@@ -5194,7 +4916,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Antoine Rodriguez</t>
+          <t>Bouigeon Tatiana</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -5203,7 +4925,6 @@
       <c r="C280" t="n">
         <v>29</v>
       </c>
-      <c r="D280" t="inlineStr"/>
       <c r="E280" t="n">
         <v>1</v>
       </c>
@@ -5211,16 +4932,15 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Bouigeon Tatiana</t>
+          <t>Emilie Olivier</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C281" t="n">
-        <v>29</v>
-      </c>
-      <c r="D281" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="E281" t="n">
         <v>1</v>
       </c>
@@ -5228,16 +4948,15 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Emilie Olivier</t>
+          <t>Sophie Decupere</t>
         </is>
       </c>
       <c r="B282" t="n">
         <v>12</v>
       </c>
       <c r="C282" t="n">
-        <v>1</v>
-      </c>
-      <c r="D282" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="E282" t="n">
         <v>1</v>
       </c>
@@ -5245,16 +4964,15 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Sophie Decupere</t>
+          <t>Roger Tg</t>
         </is>
       </c>
       <c r="B283" t="n">
         <v>12</v>
       </c>
       <c r="C283" t="n">
-        <v>2</v>
-      </c>
-      <c r="D283" t="inlineStr"/>
+        <v>4</v>
+      </c>
       <c r="E283" t="n">
         <v>1</v>
       </c>
@@ -5262,16 +4980,15 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Roger Tg</t>
+          <t>Guillaume Chaix</t>
         </is>
       </c>
       <c r="B284" t="n">
         <v>12</v>
       </c>
       <c r="C284" t="n">
-        <v>4</v>
-      </c>
-      <c r="D284" t="inlineStr"/>
+        <v>6</v>
+      </c>
       <c r="E284" t="n">
         <v>1</v>
       </c>
@@ -5279,16 +4996,15 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Guillaume Chaix</t>
+          <t>Ilan Rountree</t>
         </is>
       </c>
       <c r="B285" t="n">
         <v>12</v>
       </c>
       <c r="C285" t="n">
-        <v>6</v>
-      </c>
-      <c r="D285" t="inlineStr"/>
+        <v>7</v>
+      </c>
       <c r="E285" t="n">
         <v>1</v>
       </c>
@@ -5296,7 +5012,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Ilan Rountree</t>
+          <t>Justine Rolland</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -5305,7 +5021,6 @@
       <c r="C286" t="n">
         <v>7</v>
       </c>
-      <c r="D286" t="inlineStr"/>
       <c r="E286" t="n">
         <v>1</v>
       </c>
@@ -5313,7 +5028,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Justine Rolland</t>
+          <t>Stephanie Lakkis</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -5322,7 +5037,6 @@
       <c r="C287" t="n">
         <v>7</v>
       </c>
-      <c r="D287" t="inlineStr"/>
       <c r="E287" t="n">
         <v>1</v>
       </c>
@@ -5330,16 +5044,15 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Stephanie Lakkis</t>
+          <t>Alexandra Be Goode</t>
         </is>
       </c>
       <c r="B288" t="n">
         <v>12</v>
       </c>
       <c r="C288" t="n">
-        <v>7</v>
-      </c>
-      <c r="D288" t="inlineStr"/>
+        <v>8</v>
+      </c>
       <c r="E288" t="n">
         <v>1</v>
       </c>
@@ -5347,7 +5060,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Alexandra Be Goode</t>
+          <t>Chadia Benning</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -5356,7 +5069,6 @@
       <c r="C289" t="n">
         <v>8</v>
       </c>
-      <c r="D289" t="inlineStr"/>
       <c r="E289" t="n">
         <v>1</v>
       </c>
@@ -5364,16 +5076,15 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Chadia Benning</t>
+          <t>Julie Pernin Grandjean</t>
         </is>
       </c>
       <c r="B290" t="n">
         <v>12</v>
       </c>
       <c r="C290" t="n">
-        <v>8</v>
-      </c>
-      <c r="D290" t="inlineStr"/>
+        <v>9</v>
+      </c>
       <c r="E290" t="n">
         <v>1</v>
       </c>
@@ -5381,16 +5092,15 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Julie Pernin Grandjean</t>
+          <t>Julie Nassibou</t>
         </is>
       </c>
       <c r="B291" t="n">
         <v>12</v>
       </c>
       <c r="C291" t="n">
-        <v>9</v>
-      </c>
-      <c r="D291" t="inlineStr"/>
+        <v>11</v>
+      </c>
       <c r="E291" t="n">
         <v>1</v>
       </c>
@@ -5398,7 +5108,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Julie Nassibou</t>
+          <t>Mathilde Duperray</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -5407,7 +5117,6 @@
       <c r="C292" t="n">
         <v>11</v>
       </c>
-      <c r="D292" t="inlineStr"/>
       <c r="E292" t="n">
         <v>1</v>
       </c>
@@ -5415,16 +5124,15 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Mathilde Duperray</t>
+          <t>Charles Bdl</t>
         </is>
       </c>
       <c r="B293" t="n">
         <v>12</v>
       </c>
       <c r="C293" t="n">
-        <v>11</v>
-      </c>
-      <c r="D293" t="inlineStr"/>
+        <v>13</v>
+      </c>
       <c r="E293" t="n">
         <v>1</v>
       </c>
@@ -5432,7 +5140,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Charles Bdl</t>
+          <t>Claudio Dei Normanni</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -5441,7 +5149,6 @@
       <c r="C294" t="n">
         <v>13</v>
       </c>
-      <c r="D294" t="inlineStr"/>
       <c r="E294" t="n">
         <v>1</v>
       </c>
@@ -5449,16 +5156,15 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Claudio Dei Normanni</t>
+          <t>Benjamin Poidatz</t>
         </is>
       </c>
       <c r="B295" t="n">
         <v>12</v>
       </c>
       <c r="C295" t="n">
-        <v>13</v>
-      </c>
-      <c r="D295" t="inlineStr"/>
+        <v>16</v>
+      </c>
       <c r="E295" t="n">
         <v>1</v>
       </c>
@@ -5466,7 +5172,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Benjamin Poidatz</t>
+          <t>Nico Pom</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -5475,7 +5181,6 @@
       <c r="C296" t="n">
         <v>16</v>
       </c>
-      <c r="D296" t="inlineStr"/>
       <c r="E296" t="n">
         <v>1</v>
       </c>
@@ -5483,16 +5188,15 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Nico Pom</t>
+          <t>Marion Chan</t>
         </is>
       </c>
       <c r="B297" t="n">
         <v>12</v>
       </c>
       <c r="C297" t="n">
-        <v>16</v>
-      </c>
-      <c r="D297" t="inlineStr"/>
+        <v>17</v>
+      </c>
       <c r="E297" t="n">
         <v>1</v>
       </c>
@@ -5500,7 +5204,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Marion Chan</t>
+          <t>Myriam Af.</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -5509,7 +5213,6 @@
       <c r="C298" t="n">
         <v>17</v>
       </c>
-      <c r="D298" t="inlineStr"/>
       <c r="E298" t="n">
         <v>1</v>
       </c>
@@ -5517,16 +5220,15 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Myriam Af.</t>
+          <t>Thuvan VT</t>
         </is>
       </c>
       <c r="B299" t="n">
         <v>12</v>
       </c>
       <c r="C299" t="n">
-        <v>17</v>
-      </c>
-      <c r="D299" t="inlineStr"/>
+        <v>19</v>
+      </c>
       <c r="E299" t="n">
         <v>1</v>
       </c>
@@ -5534,16 +5236,15 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Thuvan VT</t>
+          <t>Perrine Bailly</t>
         </is>
       </c>
       <c r="B300" t="n">
         <v>12</v>
       </c>
       <c r="C300" t="n">
-        <v>19</v>
-      </c>
-      <c r="D300" t="inlineStr"/>
+        <v>20</v>
+      </c>
       <c r="E300" t="n">
         <v>1</v>
       </c>
@@ -5551,7 +5252,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Perrine Bailly</t>
+          <t>Vincent de Casabianca</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -5560,7 +5261,6 @@
       <c r="C301" t="n">
         <v>20</v>
       </c>
-      <c r="D301" t="inlineStr"/>
       <c r="E301" t="n">
         <v>1</v>
       </c>
@@ -5568,16 +5268,15 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Vincent de Casabianca</t>
+          <t>Daniel Rahal</t>
         </is>
       </c>
       <c r="B302" t="n">
         <v>12</v>
       </c>
       <c r="C302" t="n">
-        <v>20</v>
-      </c>
-      <c r="D302" t="inlineStr"/>
+        <v>22</v>
+      </c>
       <c r="E302" t="n">
         <v>1</v>
       </c>
@@ -5585,16 +5284,15 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Daniel Rahal</t>
+          <t>Emmanuelle Coros Dyen</t>
         </is>
       </c>
       <c r="B303" t="n">
         <v>12</v>
       </c>
       <c r="C303" t="n">
-        <v>22</v>
-      </c>
-      <c r="D303" t="inlineStr"/>
+        <v>23</v>
+      </c>
       <c r="E303" t="n">
         <v>1</v>
       </c>
@@ -5602,7 +5300,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Emmanuelle Coros Dyen</t>
+          <t>Mathilde Pol</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -5611,7 +5309,6 @@
       <c r="C304" t="n">
         <v>23</v>
       </c>
-      <c r="D304" t="inlineStr"/>
       <c r="E304" t="n">
         <v>1</v>
       </c>
@@ -5619,7 +5316,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Mathilde Pol</t>
+          <t>Sarah Andrieux</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -5628,7 +5325,6 @@
       <c r="C305" t="n">
         <v>23</v>
       </c>
-      <c r="D305" t="inlineStr"/>
       <c r="E305" t="n">
         <v>1</v>
       </c>
@@ -5636,16 +5332,15 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Sarah Andrieux</t>
+          <t>Marion Girard</t>
         </is>
       </c>
       <c r="B306" t="n">
         <v>12</v>
       </c>
       <c r="C306" t="n">
-        <v>23</v>
-      </c>
-      <c r="D306" t="inlineStr"/>
+        <v>24</v>
+      </c>
       <c r="E306" t="n">
         <v>1</v>
       </c>
@@ -5653,16 +5348,15 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Marion Girard</t>
+          <t>Carine Villeger</t>
         </is>
       </c>
       <c r="B307" t="n">
         <v>12</v>
       </c>
       <c r="C307" t="n">
-        <v>24</v>
-      </c>
-      <c r="D307" t="inlineStr"/>
+        <v>25</v>
+      </c>
       <c r="E307" t="n">
         <v>1</v>
       </c>
@@ -5670,7 +5364,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Carine Villeger</t>
+          <t>Laura Sg</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -5679,7 +5373,6 @@
       <c r="C308" t="n">
         <v>25</v>
       </c>
-      <c r="D308" t="inlineStr"/>
       <c r="E308" t="n">
         <v>1</v>
       </c>
@@ -5687,7 +5380,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Laura Sg</t>
+          <t>Obeid Chbicheb</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -5696,7 +5389,6 @@
       <c r="C309" t="n">
         <v>25</v>
       </c>
-      <c r="D309" t="inlineStr"/>
       <c r="E309" t="n">
         <v>1</v>
       </c>
@@ -5704,16 +5396,15 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Obeid Chbicheb</t>
+          <t>Cecile Lamy</t>
         </is>
       </c>
       <c r="B310" t="n">
         <v>12</v>
       </c>
       <c r="C310" t="n">
-        <v>25</v>
-      </c>
-      <c r="D310" t="inlineStr"/>
+        <v>30</v>
+      </c>
       <c r="E310" t="n">
         <v>1</v>
       </c>
@@ -5721,22 +5412,690 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Cecile Lamy</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C311" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Jérémy Dubs</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>2</v>
+      </c>
+      <c r="C312" t="n">
+        <v>11</v>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Florentine Montamat</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>2</v>
+      </c>
+      <c r="C313" t="n">
+        <v>12</v>
+      </c>
+      <c r="D313" t="n">
+        <v>1926</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Arthur</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>2</v>
+      </c>
+      <c r="C314" t="n">
+        <v>13</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1997</v>
+      </c>
+      <c r="E314" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Maia Dubs</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>3</v>
+      </c>
+      <c r="C315" t="n">
+        <v>2</v>
+      </c>
+      <c r="D315" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E315" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Manou</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>3</v>
+      </c>
+      <c r="C316" t="n">
+        <v>12</v>
+      </c>
+      <c r="D316" t="n">
+        <v>1936</v>
+      </c>
+      <c r="E316" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Nolan</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>3</v>
+      </c>
+      <c r="C317" t="n">
+        <v>17</v>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Simon</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>3</v>
+      </c>
+      <c r="C318" t="n">
+        <v>22</v>
+      </c>
+      <c r="D318" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E318" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Anne-Rita</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>3</v>
+      </c>
+      <c r="C319" t="n">
+        <v>25</v>
+      </c>
+      <c r="D319" t="n">
+        <v>1955</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Alain</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>4</v>
+      </c>
+      <c r="C320" t="n">
+        <v>2</v>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Céline Collin et Madalena</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>4</v>
+      </c>
+      <c r="C321" t="n">
+        <v>6</v>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Fabien</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>4</v>
+      </c>
+      <c r="C322" t="n">
+        <v>8</v>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Marc Chappellier</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>4</v>
+      </c>
+      <c r="C323" t="n">
+        <v>12</v>
+      </c>
+      <c r="D323" t="n">
+        <v>1972</v>
+      </c>
+      <c r="E323" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Sacha</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>4</v>
+      </c>
+      <c r="C324" t="n">
+        <v>13</v>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Geoges Colomb</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>4</v>
+      </c>
+      <c r="C325" t="n">
+        <v>26</v>
+      </c>
+      <c r="D325" t="n">
+        <v>1935</v>
+      </c>
+      <c r="E325" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Elie Dubs</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>5</v>
+      </c>
+      <c r="C326" t="n">
+        <v>4</v>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Elie Chappellier</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>5</v>
+      </c>
+      <c r="C327" t="n">
+        <v>4</v>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Chantal Montamat</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>5</v>
+      </c>
+      <c r="C328" t="n">
+        <v>14</v>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Anne-Solène</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>5</v>
+      </c>
+      <c r="C329" t="n">
+        <v>16</v>
+      </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Gérard Dubs</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>5</v>
+      </c>
+      <c r="C330" t="n">
+        <v>23</v>
+      </c>
+      <c r="D330" t="n">
+        <v>1951</v>
+      </c>
+      <c r="E330" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Awa</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>6</v>
+      </c>
+      <c r="C331" t="n">
+        <v>14</v>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>César</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>6</v>
+      </c>
+      <c r="C332" t="n">
+        <v>26</v>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Léna</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>6</v>
+      </c>
+      <c r="C333" t="n">
+        <v>27</v>
+      </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Dau</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>7</v>
+      </c>
+      <c r="C334" t="n">
+        <v>1</v>
+      </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>7</v>
+      </c>
+      <c r="C335" t="n">
+        <v>6</v>
+      </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>7</v>
+      </c>
+      <c r="C336" t="n">
+        <v>16</v>
+      </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Sabine Fournier</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>8</v>
+      </c>
+      <c r="C337" t="n">
+        <v>15</v>
+      </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Lucil</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>8</v>
+      </c>
+      <c r="C338" t="n">
+        <v>24</v>
+      </c>
+      <c r="D338" t="n">
+        <v>1942</v>
+      </c>
+      <c r="E338" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Sophie Nidoludo</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>9</v>
+      </c>
+      <c r="C339" t="n">
+        <v>2</v>
+      </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Myriam Tremoureux</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>9</v>
+      </c>
+      <c r="C340" t="n">
+        <v>9</v>
+      </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Vincent</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>9</v>
+      </c>
+      <c r="C341" t="n">
+        <v>18</v>
+      </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Bérangère</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>10</v>
+      </c>
+      <c r="C342" t="n">
+        <v>9</v>
+      </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Emily Dubs</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>10</v>
+      </c>
+      <c r="C343" t="n">
+        <v>11</v>
+      </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Quentin</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>10</v>
+      </c>
+      <c r="C344" t="n">
+        <v>13</v>
+      </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Serena</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>10</v>
+      </c>
+      <c r="C345" t="n">
+        <v>16</v>
+      </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Mya</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>10</v>
+      </c>
+      <c r="C346" t="n">
+        <v>21</v>
+      </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Anne Lesniczek</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>10</v>
+      </c>
+      <c r="C347" t="n">
+        <v>23</v>
+      </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Rodolphe</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>11</v>
+      </c>
+      <c r="C348" t="n">
+        <v>3</v>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Louis Dubs</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>11</v>
+      </c>
+      <c r="C349" t="n">
+        <v>15</v>
+      </c>
+      <c r="D349" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E349" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E311"/>
+  <autoFilter ref="A1:E310"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>